--- a/Data/Results/Paired/15-07-2026_to_19-07-2026/PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx
+++ b/Data/Results/Paired/15-07-2026_to_19-07-2026/PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx
@@ -72484,7 +72484,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>CAND_007</t>
+          <t>CAND_008</t>
         </is>
       </c>
     </row>
@@ -72984,7 +72984,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+          <t>COMMON_START_END_ANCHORS_FULL_INTERIOR</t>
         </is>
       </c>
     </row>
@@ -73020,7 +73020,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Continuous same-direction common route confirmed; shared start/end anchors and the hard cropped-distance tolerance are satisfied.</t>
+          <t>Common same-direction start and end anchors confirmed; the entire original cleaned telemetry section between those anchors is retained. Internal overlap/unmatched-gap metrics are audit-only, and the final cropped-distance check is satisfied.</t>
         </is>
       </c>
     </row>
@@ -73176,7 +73176,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>29-09-2026 12:15:11</t>
+          <t>06-10-2026 23:15:39</t>
         </is>
       </c>
     </row>
